--- a/tools/myCustomBlockly/iMi/CloudEspMqtt/ESP32CloudMqtt積木程式碼.xlsx
+++ b/tools/myCustomBlockly/iMi/CloudEspMqtt/ESP32CloudMqtt積木程式碼.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\maker\ArduinoMaster\tools\myCustomBlockly\iMi\CloudEspMqtt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D4B3A7-E27D-454A-A805-3DE3DFCA7BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5492454E-9709-4B95-B7B6-3DDB08354248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" tabRatio="737" firstSheet="2" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" tabRatio="737" firstSheet="2" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="S(變)" sheetId="7" r:id="rId1"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="153">
   <si>
     <t>SETUP區 連N拉N</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1779,9 +1779,6 @@
     <t xml:space="preserve">  msgXY[1] = (char)payload[1]; </t>
   </si>
   <si>
-    <t xml:space="preserve">  msgXY[2] = \'\0\';</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Serial.println(msgXY);</t>
   </si>
   <si>
@@ -1815,6 +1812,13 @@
       </rPr>
       <t>'</t>
     </r>
+  </si>
+  <si>
+    <t>_06imi_mqttcloud_submqtt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  msgXY[2] = \'\\0\';</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -7421,7 +7425,7 @@
       </c>
       <c r="D1" s="7" t="str">
         <f>"Blockly.Arduino.setups_['"&amp;D2&amp;"'] = '"&amp;D3&amp;"';"</f>
-        <v>Blockly.Arduino.setups_[''] = '  //訂閱\n  client.subscribe(TOPIC_CAR_GPS);\n  Serial.println(String(TOPIC_CAR_GPS)+"已訂閱成功！請開啟https://console.hivemq.cloud/，並用Publish Message來測試！");\n';</v>
+        <v>Blockly.Arduino.setups_['_06imi_mqttcloud_submqtt'] = '  //訂閱\n  client.subscribe(TOPIC_CAR_GPS);\n  Serial.println(String(TOPIC_CAR_GPS)+"已訂閱成功！請開啟https://console.hivemq.cloud/，並用Publish Message來測試！");\n';</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -7448,7 +7452,9 @@
       <c r="C2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="32"/>
+      <c r="D2" s="32" t="s">
+        <v>151</v>
+      </c>
       <c r="E2" s="13"/>
       <c r="F2" s="10"/>
     </row>
@@ -8367,7 +8373,7 @@
       </c>
       <c r="H1" s="7" t="str">
         <f>"Blockly.Arduino.functions_['"&amp;H2&amp;"'] = '"&amp;H3&amp;"' + "&amp;H4&amp;" + '"&amp;H5&amp;"';"</f>
-        <v>Blockly.Arduino.functions_['_07imi_mqttcloud_mqttcallback_func'] = '//MQTT訂閱的主題回覆\n void callback(char* topic, byte* payload, unsigned int length) {\n   //傳送至ESP32 GPS板(格式:xy)\n   msgXY[0] = (char)payload[0];\n   msgXY[1] = (char)payload[1]; \n   msgXY[2] = \'\0\';\n   Serial.println(msgXY);\n ' + statements_msg + '}\n ';</v>
+        <v>Blockly.Arduino.functions_['_07imi_mqttcloud_mqttcallback_func'] = '//MQTT訂閱的主題回覆\n void callback(char* topic, byte* payload, unsigned int length) {\n   //傳送至ESP32 GPS板(格式:xy)\n   msgXY[0] = (char)payload[0];\n   msgXY[1] = (char)payload[1]; \n   msgXY[2] = \'\\0\';\n   Serial.println(msgXY);\n ' + statements_msg + '}\n ';</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -8422,7 +8428,7 @@
       </c>
       <c r="H3" s="5" t="str">
         <f>_xlfn.CONCAT(B2:B999)</f>
-        <v xml:space="preserve">//MQTT訂閱的主題回覆\n void callback(char* topic, byte* payload, unsigned int length) {\n   //傳送至ESP32 GPS板(格式:xy)\n   msgXY[0] = (char)payload[0];\n   msgXY[1] = (char)payload[1]; \n   msgXY[2] = \'\0\';\n   Serial.println(msgXY);\n </v>
+        <v xml:space="preserve">//MQTT訂閱的主題回覆\n void callback(char* topic, byte* payload, unsigned int length) {\n   //傳送至ESP32 GPS板(格式:xy)\n   msgXY[0] = (char)payload[0];\n   msgXY[1] = (char)payload[1]; \n   msgXY[2] = \'\\0\';\n   Serial.println(msgXY);\n </v>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="22"/>
@@ -8502,11 +8508,11 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B7" s="18" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">  msgXY[2] = \'\0\';\n </v>
+        <v xml:space="preserve">  msgXY[2] = \'\\0\';\n </v>
       </c>
       <c r="C7" s="20"/>
       <c r="D7" s="18" t="str">
@@ -8521,7 +8527,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B8" s="18" t="str">
         <f t="shared" si="0"/>
@@ -9973,7 +9979,7 @@
       </c>
       <c r="H2" s="25"/>
       <c r="I2" s="28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J2" s="18" t="str">
         <f>IF(ISBLANK(I2),"",I2&amp;"+'\n'+")</f>
